--- a/data/ams_weekly_data/Nexlev/ads_report_week33.xlsx
+++ b/data/ams_weekly_data/Nexlev/ads_report_week33.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SP" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SD" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SB" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="SP" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="SD" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="SB" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,16 +19,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -39,7 +36,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -47,21 +44,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -431,42 +419,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Portfolio name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Campaign Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Advertised ASIN</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Clicks</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Impressions</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>14 Day Total Sales (₹)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>14 Day Total Units (#)</t>
         </is>
@@ -553,7 +541,7 @@
         <v>3969.53</v>
       </c>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -1023,7 +1011,7 @@
         <v>57</v>
       </c>
       <c r="F21" t="n">
-        <v>31028</v>
+        <v>31026</v>
       </c>
       <c r="G21" t="n">
         <v>1558.47</v>
@@ -1505,7 +1493,7 @@
         <v>8258.470000000001</v>
       </c>
       <c r="H38" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39">
@@ -1586,10 +1574,10 @@
         <v>59462</v>
       </c>
       <c r="G41" t="n">
-        <v>14479.67</v>
+        <v>16266.96</v>
       </c>
       <c r="H41" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="42">
@@ -1639,7 +1627,7 @@
         <v>95</v>
       </c>
       <c r="F43" t="n">
-        <v>36982</v>
+        <v>36980</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -2062,10 +2050,10 @@
         <v>6676</v>
       </c>
       <c r="G58" t="n">
-        <v>44166.94</v>
+        <v>39083.04</v>
       </c>
       <c r="H58" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="59">
@@ -2398,10 +2386,10 @@
         <v>15303</v>
       </c>
       <c r="G70" t="n">
-        <v>8504.24</v>
+        <v>10198.31</v>
       </c>
       <c r="H70" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="71">
@@ -2955,7 +2943,7 @@
         <v>271</v>
       </c>
       <c r="F90" t="n">
-        <v>84632</v>
+        <v>84630</v>
       </c>
       <c r="G90" t="n">
         <v>32505.94</v>
@@ -4803,7 +4791,7 @@
         <v>131</v>
       </c>
       <c r="F156" t="n">
-        <v>13037</v>
+        <v>13035</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -5363,7 +5351,7 @@
         <v>19</v>
       </c>
       <c r="F176" t="n">
-        <v>6932</v>
+        <v>6931</v>
       </c>
       <c r="G176" t="n">
         <v>10168.64</v>
@@ -6010,10 +5998,10 @@
         <v>1836</v>
       </c>
       <c r="G199" t="n">
-        <v>420.33</v>
+        <v>630.5</v>
       </c>
       <c r="H199" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="200">
@@ -6287,7 +6275,7 @@
         <v>19</v>
       </c>
       <c r="F209" t="n">
-        <v>3791</v>
+        <v>3790</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -10179,7 +10167,7 @@
         <v>210</v>
       </c>
       <c r="F348" t="n">
-        <v>66928</v>
+        <v>66927</v>
       </c>
       <c r="G348" t="n">
         <v>4573.74</v>
@@ -10798,10 +10786,10 @@
         <v>15058</v>
       </c>
       <c r="G370" t="n">
-        <v>3472.88</v>
+        <v>5251.69</v>
       </c>
       <c r="H370" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="371">
@@ -10987,42 +10975,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Portfolio name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Campaign Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Advertised ASIN</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Clicks</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Impressions</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>14 Day Total Sales (₹)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>14 Day Total Units (#)</t>
         </is>
@@ -12303,47 +12291,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Portfolio name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Campaign Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Advertised ASIN</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Impressions</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Clicks</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>14 Day Total Sales (₹)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>14 Day Total Units (#)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
@@ -12404,10 +12392,10 @@
         <v>5604.23</v>
       </c>
       <c r="G3" t="n">
-        <v>44120.34</v>
+        <v>47509.32</v>
       </c>
       <c r="H3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -12764,7 +12752,7 @@
         <v>2</v>
       </c>
       <c r="F14" t="n">
-        <v>19.28272082014246</v>
+        <v>19.28272082014247</v>
       </c>
       <c r="G14" t="n">
         <v>308.8038056019913</v>
@@ -12800,7 +12788,7 @@
         <v>238.5505200036836</v>
       </c>
       <c r="G15" t="n">
-        <v>3820.27562876509</v>
+        <v>3820.275628765091</v>
       </c>
       <c r="H15" t="n">
         <v>1</v>
@@ -12998,10 +12986,10 @@
         <v>12449.1060780496</v>
       </c>
       <c r="G21" t="n">
-        <v>199852.9704890235</v>
+        <v>211255.0332869278</v>
       </c>
       <c r="H21" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -13031,10 +13019,10 @@
         <v>7903.700420290515</v>
       </c>
       <c r="G22" t="n">
-        <v>126882.8458001119</v>
+        <v>134121.7983773474</v>
       </c>
       <c r="H22" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -13064,7 +13052,7 @@
         <v>17.76781670811666</v>
       </c>
       <c r="G23" t="n">
-        <v>285.2374239530896</v>
+        <v>301.5108624327254</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -13097,10 +13085,10 @@
         <v>3439.645684951773</v>
       </c>
       <c r="G24" t="n">
-        <v>55218.69628691143</v>
+        <v>58369.04747329197</v>
       </c>
       <c r="H24" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
